--- a/output/2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore 'one-stop' di hardware industriale (power tools, pneumatica, saldatura, fissaggi); rivende marchi Bosch, Toyox, Nachi, Stanley. Verificato via sito ufficiale.</t>
+          <t>Distributore 'one-stop' di hardware industriale (power tools, pneumatica, saldatura, fissaggi); rivende marchi Bosch, Toyox, Nachi, Stanley. Verificato via sito ufficiale. [DUPLICATO — vedi anche: 2026-10-02_01_Malesia_Melaka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,7 +536,6 @@
           <t>06-335 6992 / 06-335 6995 (fax 06-335 6551)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Sito non raggiungibile (DNS fail); verificato tramite fonti terze (directory di settore) con indirizzo/telefono coincidenti. Distributore esclusivo marchi PRECISE/VIEW MASTER per strumentazione di misura di precisione.</t>
@@ -544,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -712,7 +711,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -784,7 +783,6 @@
           <t>+606-335 1000 / +606-337 3002 / +606-336 5002 / +606-334 6000</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Distributore regionale di cuscinetti NSK, ball screw e automazione; sede centrale a Ipoh, Perak. Melaka elencata tra le filiali ufficiali sul sito.</t>
@@ -876,7 +874,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -913,7 +911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Filiale Melaka (Jalan MP3, Taman Merdeka Permai) confermata; sede principale in Selangor dal 1996; fornitore di componenti idraulici/pneumatici.</t>
+          <t>Filiale Melaka (Jalan MP3, Taman Merdeka Permai) confermata; sede principale in Selangor dal 1996; fornitore di componenti idraulici/pneumatici. [DUPLICATO — vedi anche: 2026-10-01_22_Malesia_Melaka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -928,7 +926,6 @@
           <t>Systech Industrial Supplies</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Melaka</t>
@@ -966,7 +963,6 @@
           <t>Rexpower Sdn Bhd</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Melaka</t>
@@ -982,7 +978,6 @@
           <t>06-2848148 (fax 06-2849904)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Nessun sito ufficiale proprio trovato. Confermata tramite Waze (indirizzo esatto) e Malacca Chinese Chamber of Commerce (membro LB146). Fornitore di valvole idrauliche/pneumatiche, pompe.</t>
@@ -1104,10 +1099,9 @@
           <t>+606-3338889 / +606-3338887 / +606-3338898 (fax +606-3338899)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Filiale Melaka confermata all'indirizzo Jalan PB 1B, Taman Puncak Bertam, 75250 Melaka.</t>
+          <t>Filiale Melaka confermata all'indirizzo Jalan PB 1B, Taman Puncak Bertam, 75250 Melaka. [DUPLICATO — vedi anche: 2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1154,7 +1148,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-02_03_Malesia_Melaka_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sede centrale a Penang (dal 1993); filiale Melaka confermata nella rete di uffici regionali del sito ufficiale.</t>
+          <t>Sede centrale a Penang (dal 1993); filiale Melaka confermata nella rete di uffici regionali del sito ufficiale. [DUPLICATO — vedi anche: 2026-09-30_22_Malesia_Johor_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
